--- a/grupos/3BEM - Estadisticos 20241.xlsx
+++ b/grupos/3BEM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="109">
   <si>
     <t>Materia</t>
   </si>
@@ -179,15 +179,15 @@
     <t>Velasco Sánchez David</t>
   </si>
   <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
     <t>Marin Arzaba Roberto</t>
   </si>
   <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
@@ -203,45 +203,48 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>ECHAVARRIA</t>
+  </si>
+  <si>
+    <t>ESCOBEDO</t>
+  </si>
+  <si>
     <t>GOMEZ</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OROZCO</t>
+  </si>
+  <si>
     <t>SAAVEDRA</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>ECHAVARRIA</t>
-  </si>
-  <si>
-    <t>ESCOBEDO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OROZCO</t>
-  </si>
-  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
@@ -251,82 +254,88 @@
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>DURAND</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
     <t>GUERRA</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>DURAND</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
     <t>URBINA</t>
   </si>
   <si>
     <t>CALIHUA</t>
   </si>
   <si>
+    <t>IAN</t>
+  </si>
+  <si>
+    <t>NAIDELYN</t>
+  </si>
+  <si>
+    <t>ELIAS IGNACIO</t>
+  </si>
+  <si>
+    <t>JOSE GUADALUPE</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>KEVIN SANTIAGO</t>
+  </si>
+  <si>
+    <t>JOSE EMMANUEL</t>
+  </si>
+  <si>
     <t>ANGEL GABRIEL</t>
   </si>
   <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>JAZIEL</t>
+  </si>
+  <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOANNA OCTAVIA</t>
+  </si>
+  <si>
     <t>JOSE ARTURO</t>
-  </si>
-  <si>
-    <t>NAIDELYN</t>
-  </si>
-  <si>
-    <t>ELIAS IGNACIO</t>
-  </si>
-  <si>
-    <t>JOSE GUADALUPE</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>KEVIN SANTIAGO</t>
-  </si>
-  <si>
-    <t>JOSE EMMANUEL</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>JAZIEL</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOANNA OCTAVIA</t>
   </si>
   <si>
     <t>ARELY SUSANA</t>
@@ -881,28 +890,28 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -935,16 +944,16 @@
         <v>7</v>
       </c>
       <c r="AB4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC4">
         <v>5</v>
       </c>
       <c r="AD4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF4">
         <v>5</v>
@@ -982,28 +991,28 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1030,7 +1039,7 @@
         <v>-1</v>
       </c>
       <c r="Z5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA5">
         <v>8</v>
@@ -1039,10 +1048,10 @@
         <v>6</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE5">
         <v>8</v>
@@ -1083,28 +1092,28 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1131,13 +1140,13 @@
         <v>-1</v>
       </c>
       <c r="Z6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA6">
         <v>9</v>
       </c>
       <c r="AB6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC6">
         <v>8</v>
@@ -1184,28 +1193,28 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1232,22 +1241,22 @@
         <v>-1</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA7">
         <v>7</v>
       </c>
       <c r="AB7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC7">
         <v>5</v>
       </c>
       <c r="AD7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF7">
         <v>5</v>
@@ -1285,28 +1294,28 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1333,7 +1342,7 @@
         <v>-1</v>
       </c>
       <c r="Z8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA8">
         <v>10</v>
@@ -1342,13 +1351,13 @@
         <v>6</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF8">
         <v>6</v>
@@ -1386,28 +1395,28 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1487,28 +1496,28 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1535,7 +1544,7 @@
         <v>-1</v>
       </c>
       <c r="Z10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA10">
         <v>7</v>
@@ -1544,13 +1553,13 @@
         <v>7</v>
       </c>
       <c r="AC10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF10">
         <v>7</v>
@@ -1588,28 +1597,28 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1636,19 +1645,19 @@
         <v>-1</v>
       </c>
       <c r="Z11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA11">
         <v>8</v>
       </c>
       <c r="AB11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC11">
         <v>8</v>
       </c>
       <c r="AD11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE11">
         <v>8</v>
@@ -1689,28 +1698,28 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1737,19 +1746,19 @@
         <v>-1</v>
       </c>
       <c r="Z12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA12">
         <v>8</v>
       </c>
       <c r="AB12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE12">
         <v>8</v>
@@ -1790,28 +1799,28 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1838,22 +1847,22 @@
         <v>-1</v>
       </c>
       <c r="Z13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA13">
         <v>9</v>
       </c>
       <c r="AB13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF13">
         <v>7</v>
@@ -1891,28 +1900,28 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1939,22 +1948,22 @@
         <v>-1</v>
       </c>
       <c r="Z14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA14">
         <v>7</v>
       </c>
       <c r="AB14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC14">
         <v>7</v>
       </c>
       <c r="AD14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF14">
         <v>7</v>
@@ -1992,28 +2001,28 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -2040,22 +2049,22 @@
         <v>-1</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA15">
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC15">
         <v>5</v>
       </c>
       <c r="AD15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF15">
         <v>5</v>
@@ -2093,28 +2102,28 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2141,7 +2150,7 @@
         <v>-1</v>
       </c>
       <c r="Z16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA16">
         <v>10</v>
@@ -2150,13 +2159,13 @@
         <v>10</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD16">
         <v>10</v>
       </c>
       <c r="AE16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF16">
         <v>10</v>
@@ -2194,28 +2203,28 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2242,22 +2251,22 @@
         <v>-1</v>
       </c>
       <c r="Z17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA17">
         <v>8</v>
       </c>
       <c r="AB17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC17">
         <v>5</v>
       </c>
       <c r="AD17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF17">
         <v>5</v>
@@ -2295,28 +2304,28 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2355,10 +2364,10 @@
         <v>7</v>
       </c>
       <c r="AD18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF18">
         <v>8</v>
@@ -2396,28 +2405,28 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2453,13 +2462,13 @@
         <v>10</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD19">
         <v>9</v>
       </c>
       <c r="AE19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF19">
         <v>8</v>
@@ -2497,28 +2506,28 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2545,13 +2554,13 @@
         <v>-1</v>
       </c>
       <c r="Z20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA20">
         <v>10</v>
       </c>
       <c r="AB20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC20">
         <v>10</v>
@@ -2560,7 +2569,7 @@
         <v>10</v>
       </c>
       <c r="AE20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF20">
         <v>10</v>
@@ -2598,28 +2607,28 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2646,13 +2655,13 @@
         <v>-1</v>
       </c>
       <c r="Z21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA21">
         <v>8</v>
       </c>
       <c r="AB21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>5</v>
@@ -2699,28 +2708,28 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2747,7 +2756,7 @@
         <v>-1</v>
       </c>
       <c r="Z22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -2800,28 +2809,28 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2848,22 +2857,22 @@
         <v>-1</v>
       </c>
       <c r="Z23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA23">
         <v>7</v>
       </c>
       <c r="AB23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC23">
         <v>5</v>
       </c>
       <c r="AD23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF23">
         <v>7</v>
@@ -2901,28 +2910,28 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2949,22 +2958,22 @@
         <v>-1</v>
       </c>
       <c r="Z24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA24">
         <v>10</v>
       </c>
       <c r="AB24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF24">
         <v>10</v>
@@ -3002,28 +3011,28 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -3103,28 +3112,28 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -3151,22 +3160,22 @@
         <v>-1</v>
       </c>
       <c r="Z26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA26">
         <v>7</v>
       </c>
       <c r="AB26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF26">
         <v>6</v>
@@ -3204,28 +3213,28 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -3252,19 +3261,19 @@
         <v>-1</v>
       </c>
       <c r="Z27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA27">
         <v>5</v>
       </c>
       <c r="AB27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC27">
         <v>5</v>
       </c>
       <c r="AD27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE27">
         <v>8</v>
@@ -3448,7 +3457,7 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>72.2</v>
+        <v>75.8</v>
       </c>
       <c r="N4">
         <v>100</v>
@@ -3472,7 +3481,7 @@
         <v>100</v>
       </c>
       <c r="U4">
-        <v>72.2</v>
+        <v>75.8</v>
       </c>
       <c r="V4">
         <v>100</v>
@@ -3525,13 +3534,13 @@
         <v>100</v>
       </c>
       <c r="M5">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N5">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="O5">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -3549,13 +3558,13 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="V5">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="W5">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="X5">
         <v>100</v>
@@ -3679,7 +3688,7 @@
         <v>100</v>
       </c>
       <c r="M7">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N7">
         <v>100</v>
@@ -3703,7 +3712,7 @@
         <v>100</v>
       </c>
       <c r="U7">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -3756,7 +3765,7 @@
         <v>100</v>
       </c>
       <c r="M8">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N8">
         <v>100</v>
@@ -3780,7 +3789,7 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -3910,10 +3919,10 @@
         <v>100</v>
       </c>
       <c r="M10">
-        <v>88.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N10">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -3934,10 +3943,10 @@
         <v>100</v>
       </c>
       <c r="U10">
-        <v>88.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="V10">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="W10">
         <v>100</v>
@@ -3987,7 +3996,7 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N11">
         <v>100</v>
@@ -4011,7 +4020,7 @@
         <v>100</v>
       </c>
       <c r="U11">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="V11">
         <v>100</v>
@@ -4064,10 +4073,10 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N12">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -4088,10 +4097,10 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="V12">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="W12">
         <v>100</v>
@@ -4141,10 +4150,10 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N13">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -4165,10 +4174,10 @@
         <v>100</v>
       </c>
       <c r="U13">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="V13">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="W13">
         <v>100</v>
@@ -4218,13 +4227,13 @@
         <v>100</v>
       </c>
       <c r="M14">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N14">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O14">
-        <v>98.3</v>
+        <v>99.2</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -4242,13 +4251,13 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="V14">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="W14">
-        <v>98.3</v>
+        <v>99.2</v>
       </c>
       <c r="X14">
         <v>100</v>
@@ -4295,13 +4304,13 @@
         <v>100</v>
       </c>
       <c r="M15">
-        <v>88.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N15">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O15">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P15">
         <v>95</v>
@@ -4319,13 +4328,13 @@
         <v>100</v>
       </c>
       <c r="U15">
-        <v>88.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="V15">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="W15">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="X15">
         <v>95</v>
@@ -4449,7 +4458,7 @@
         <v>100</v>
       </c>
       <c r="M17">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N17">
         <v>100</v>
@@ -4473,7 +4482,7 @@
         <v>100</v>
       </c>
       <c r="U17">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -4532,7 +4541,7 @@
         <v>100</v>
       </c>
       <c r="O18">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P18">
         <v>95</v>
@@ -4556,7 +4565,7 @@
         <v>100</v>
       </c>
       <c r="W18">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="X18">
         <v>95</v>
@@ -4603,7 +4612,7 @@
         <v>100</v>
       </c>
       <c r="M19">
-        <v>88.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N19">
         <v>100</v>
@@ -4627,7 +4636,7 @@
         <v>100</v>
       </c>
       <c r="U19">
-        <v>88.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -4680,7 +4689,7 @@
         <v>100</v>
       </c>
       <c r="M20">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N20">
         <v>100</v>
@@ -4704,7 +4713,7 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -4757,13 +4766,13 @@
         <v>100</v>
       </c>
       <c r="M21">
-        <v>94.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N21">
         <v>100</v>
       </c>
       <c r="O21">
-        <v>98.3</v>
+        <v>99.2</v>
       </c>
       <c r="P21">
         <v>85</v>
@@ -4781,13 +4790,13 @@
         <v>100</v>
       </c>
       <c r="U21">
-        <v>94.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="V21">
         <v>100</v>
       </c>
       <c r="W21">
-        <v>98.3</v>
+        <v>99.2</v>
       </c>
       <c r="X21">
         <v>85</v>
@@ -4834,13 +4843,13 @@
         <v>100</v>
       </c>
       <c r="M22">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="N22">
         <v>100</v>
       </c>
       <c r="O22">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -4858,13 +4867,13 @@
         <v>100</v>
       </c>
       <c r="U22">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="V22">
         <v>100</v>
       </c>
       <c r="W22">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="X22">
         <v>100</v>
@@ -4911,10 +4920,10 @@
         <v>100</v>
       </c>
       <c r="M23">
-        <v>83.3</v>
+        <v>84.8</v>
       </c>
       <c r="N23">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="O23">
         <v>100</v>
@@ -4935,10 +4944,10 @@
         <v>100</v>
       </c>
       <c r="U23">
-        <v>83.3</v>
+        <v>84.8</v>
       </c>
       <c r="V23">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="W23">
         <v>100</v>
@@ -5142,10 +5151,10 @@
         <v>100</v>
       </c>
       <c r="M26">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="N26">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -5166,10 +5175,10 @@
         <v>100</v>
       </c>
       <c r="U26">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="V26">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="W26">
         <v>100</v>
@@ -5219,13 +5228,13 @@
         <v>100</v>
       </c>
       <c r="M27">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="N27">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O27">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P27">
         <v>75</v>
@@ -5243,13 +5252,13 @@
         <v>100</v>
       </c>
       <c r="U27">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="V27">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="W27">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="X27">
         <v>75</v>
@@ -5362,7 +5371,7 @@
         <v>29.2</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5405,7 +5414,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>53</v>
@@ -5414,19 +5423,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>87.5</v>
+        <v>95.8</v>
       </c>
       <c r="G5" s="2">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5446,19 +5455,19 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="G6" s="2">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5469,7 +5478,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
@@ -5478,19 +5487,19 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5501,25 +5510,25 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8">
         <v>24</v>
       </c>
       <c r="D8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="G8" s="2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>8</v>
@@ -5533,10 +5542,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C9">
         <v>24</v>
@@ -5554,7 +5563,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -5636,22 +5645,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920232</v>
+        <v>23330051920043</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5659,16 +5668,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920232</v>
+        <v>23330051920043</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -5682,39 +5691,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920044</v>
+        <v>23330051920029</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920044</v>
+        <v>23330051920031</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -5728,16 +5737,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920029</v>
+        <v>23330051920030</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
         <v>12</v>
@@ -5751,16 +5760,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920031</v>
+        <v>22330051920007</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -5774,16 +5783,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920030</v>
+        <v>23330051920033</v>
       </c>
       <c r="B8" t="s">
         <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
@@ -5797,16 +5806,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920007</v>
+        <v>23330051920034</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
@@ -5820,16 +5829,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920033</v>
+        <v>23330051920232</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
@@ -5843,16 +5852,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920034</v>
+        <v>23330051920035</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
@@ -5866,16 +5875,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920035</v>
+        <v>23330051920032</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
@@ -5889,16 +5898,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920032</v>
+        <v>23330051920039</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
@@ -5912,16 +5921,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920039</v>
+        <v>23330051920040</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
         <v>12</v>
@@ -5935,16 +5944,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920040</v>
+        <v>23330051920041</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
@@ -5958,16 +5967,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920041</v>
+        <v>23330051920042</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E16" t="s">
         <v>12</v>
@@ -5981,16 +5990,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920042</v>
+        <v>23330051920044</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E17" t="s">
         <v>12</v>
@@ -6007,13 +6016,13 @@
         <v>23330051920209</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E18" t="s">
         <v>12</v>
@@ -6030,13 +6039,13 @@
         <v>23330051920210</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
         <v>12</v>
@@ -6053,13 +6062,13 @@
         <v>23330051920046</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E20" t="s">
         <v>12</v>

--- a/grupos/3BEM - Estadisticos 20241.xlsx
+++ b/grupos/3BEM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="114">
   <si>
     <t>Materia</t>
   </si>
@@ -179,12 +179,12 @@
     <t>Velasco Sánchez David</t>
   </si>
   <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
     <t>Castro Vasquez Julieta</t>
   </si>
   <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
     <t>Marin Arzaba Roberto</t>
   </si>
   <si>
@@ -203,10 +203,16 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>CARRERA</t>
+    <t>VERA</t>
   </si>
   <si>
     <t>COYOHUA</t>
@@ -254,10 +260,16 @@
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>SOLANO</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>VILLA</t>
   </si>
   <si>
     <t>IXMATLAHUA</t>
@@ -275,9 +287,6 @@
     <t>HUERTA</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
     <t>MIXCOA</t>
   </si>
   <si>
@@ -293,9 +302,18 @@
     <t>CALIHUA</t>
   </si>
   <si>
+    <t>JESUS JAREF</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
     <t>IAN</t>
   </si>
   <si>
+    <t>ALEX URIEL</t>
+  </si>
+  <si>
     <t>NAIDELYN</t>
   </si>
   <si>
@@ -303,9 +321,6 @@
   </si>
   <si>
     <t>JOSE GUADALUPE</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
   </si>
   <si>
     <t>KEVIN SANTIAGO</t>
@@ -893,7 +908,7 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>7</v>
@@ -908,7 +923,7 @@
         <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
         <v>10</v>
@@ -941,7 +956,7 @@
         <v>8</v>
       </c>
       <c r="AA4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB4">
         <v>7</v>
@@ -994,7 +1009,7 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>6</v>
@@ -1009,7 +1024,7 @@
         <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
         <v>10</v>
@@ -1057,7 +1072,7 @@
         <v>8</v>
       </c>
       <c r="AF5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG5">
         <v>-1</v>
@@ -1095,7 +1110,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>7</v>
@@ -1110,7 +1125,7 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>10</v>
@@ -1158,7 +1173,7 @@
         <v>9</v>
       </c>
       <c r="AF6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG6">
         <v>-1</v>
@@ -1196,7 +1211,7 @@
         <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>7</v>
@@ -1211,7 +1226,7 @@
         <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>10</v>
@@ -1244,7 +1259,7 @@
         <v>9</v>
       </c>
       <c r="AA7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB7">
         <v>7</v>
@@ -1259,7 +1274,7 @@
         <v>7</v>
       </c>
       <c r="AF7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG7">
         <v>-1</v>
@@ -1297,7 +1312,7 @@
         <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>6</v>
@@ -1312,7 +1327,7 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
         <v>10</v>
@@ -1398,7 +1413,7 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -1413,7 +1428,7 @@
         <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
         <v>10</v>
@@ -1499,7 +1514,7 @@
         <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
         <v>7</v>
@@ -1514,7 +1529,7 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -1547,7 +1562,7 @@
         <v>8</v>
       </c>
       <c r="AA10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB10">
         <v>7</v>
@@ -1600,7 +1615,7 @@
         <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -1615,7 +1630,7 @@
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
         <v>10</v>
@@ -1648,7 +1663,7 @@
         <v>8</v>
       </c>
       <c r="AA11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB11">
         <v>9</v>
@@ -1701,7 +1716,7 @@
         <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>10</v>
@@ -1716,7 +1731,7 @@
         <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
         <v>10</v>
@@ -1749,7 +1764,7 @@
         <v>10</v>
       </c>
       <c r="AA12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB12">
         <v>9</v>
@@ -1802,7 +1817,7 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -1817,7 +1832,7 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>10</v>
@@ -1850,7 +1865,7 @@
         <v>9</v>
       </c>
       <c r="AA13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB13">
         <v>8</v>
@@ -1865,7 +1880,7 @@
         <v>7</v>
       </c>
       <c r="AF13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG13">
         <v>-1</v>
@@ -1903,7 +1918,7 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>7</v>
@@ -1918,7 +1933,7 @@
         <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
         <v>10</v>
@@ -1951,7 +1966,7 @@
         <v>10</v>
       </c>
       <c r="AA14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB14">
         <v>7</v>
@@ -2004,7 +2019,7 @@
         <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>9</v>
@@ -2019,7 +2034,7 @@
         <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>10</v>
@@ -2052,7 +2067,7 @@
         <v>8</v>
       </c>
       <c r="AA15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB15">
         <v>8</v>
@@ -2105,7 +2120,7 @@
         <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>10</v>
@@ -2120,7 +2135,7 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
         <v>10</v>
@@ -2206,7 +2221,7 @@
         <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
         <v>10</v>
@@ -2221,7 +2236,7 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
         <v>10</v>
@@ -2254,7 +2269,7 @@
         <v>10</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB17">
         <v>8</v>
@@ -2307,7 +2322,7 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -2322,7 +2337,7 @@
         <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
         <v>10</v>
@@ -2355,7 +2370,7 @@
         <v>10</v>
       </c>
       <c r="AA18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB18">
         <v>10</v>
@@ -2370,7 +2385,7 @@
         <v>8</v>
       </c>
       <c r="AF18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG18">
         <v>-1</v>
@@ -2408,7 +2423,7 @@
         <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
         <v>10</v>
@@ -2423,7 +2438,7 @@
         <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -2471,7 +2486,7 @@
         <v>9</v>
       </c>
       <c r="AF19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG19">
         <v>-1</v>
@@ -2509,7 +2524,7 @@
         <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
         <v>8</v>
@@ -2524,7 +2539,7 @@
         <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -2610,7 +2625,7 @@
         <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>10</v>
@@ -2625,7 +2640,7 @@
         <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
         <v>10</v>
@@ -2658,7 +2673,7 @@
         <v>8</v>
       </c>
       <c r="AA21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB21">
         <v>8</v>
@@ -2711,7 +2726,7 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -2726,7 +2741,7 @@
         <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -2774,7 +2789,7 @@
         <v>8</v>
       </c>
       <c r="AF22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG22">
         <v>-1</v>
@@ -2812,7 +2827,7 @@
         <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>5</v>
@@ -2827,7 +2842,7 @@
         <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
         <v>10</v>
@@ -2860,7 +2875,7 @@
         <v>8</v>
       </c>
       <c r="AA23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>5</v>
@@ -2913,7 +2928,7 @@
         <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>6</v>
@@ -2928,7 +2943,7 @@
         <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
         <v>10</v>
@@ -3014,7 +3029,7 @@
         <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -3029,7 +3044,7 @@
         <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -3115,7 +3130,7 @@
         <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>8</v>
@@ -3130,7 +3145,7 @@
         <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
         <v>10</v>
@@ -3163,7 +3178,7 @@
         <v>9</v>
       </c>
       <c r="AA26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB26">
         <v>7</v>
@@ -3216,7 +3231,7 @@
         <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
         <v>8</v>
@@ -3231,7 +3246,7 @@
         <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
         <v>10</v>
@@ -3264,7 +3279,7 @@
         <v>8</v>
       </c>
       <c r="AA27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB27">
         <v>7</v>
@@ -3279,7 +3294,7 @@
         <v>8</v>
       </c>
       <c r="AF27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG27">
         <v>-1</v>
@@ -3466,7 +3481,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>85</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -3490,7 +3505,7 @@
         <v>100</v>
       </c>
       <c r="X4">
-        <v>85</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Y4">
         <v>100</v>
@@ -3543,7 +3558,7 @@
         <v>98.3</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -3567,7 +3582,7 @@
         <v>98.3</v>
       </c>
       <c r="X5">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y5">
         <v>100</v>
@@ -3697,7 +3712,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -3721,7 +3736,7 @@
         <v>100</v>
       </c>
       <c r="X7">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Y7">
         <v>100</v>
@@ -3928,7 +3943,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>85</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -3952,7 +3967,7 @@
         <v>100</v>
       </c>
       <c r="X10">
-        <v>85</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Y10">
         <v>100</v>
@@ -4005,7 +4020,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -4029,7 +4044,7 @@
         <v>100</v>
       </c>
       <c r="X11">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Y11">
         <v>100</v>
@@ -4082,7 +4097,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4106,7 +4121,7 @@
         <v>100</v>
       </c>
       <c r="X12">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y12">
         <v>100</v>
@@ -4159,7 +4174,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>90</v>
+        <v>93.2</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -4183,7 +4198,7 @@
         <v>100</v>
       </c>
       <c r="X13">
-        <v>90</v>
+        <v>93.2</v>
       </c>
       <c r="Y13">
         <v>100</v>
@@ -4236,7 +4251,7 @@
         <v>99.2</v>
       </c>
       <c r="P14">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -4260,7 +4275,7 @@
         <v>99.2</v>
       </c>
       <c r="X14">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y14">
         <v>100</v>
@@ -4313,7 +4328,7 @@
         <v>98.3</v>
       </c>
       <c r="P15">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4337,7 +4352,7 @@
         <v>98.3</v>
       </c>
       <c r="X15">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="Y15">
         <v>100</v>
@@ -4467,7 +4482,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>85</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -4491,7 +4506,7 @@
         <v>100</v>
       </c>
       <c r="X17">
-        <v>85</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Y17">
         <v>100</v>
@@ -4544,7 +4559,7 @@
         <v>98.3</v>
       </c>
       <c r="P18">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -4568,7 +4583,7 @@
         <v>98.3</v>
       </c>
       <c r="X18">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="Y18">
         <v>100</v>
@@ -4775,7 +4790,7 @@
         <v>99.2</v>
       </c>
       <c r="P21">
-        <v>85</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -4799,7 +4814,7 @@
         <v>99.2</v>
       </c>
       <c r="X21">
-        <v>85</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Y21">
         <v>100</v>
@@ -4852,7 +4867,7 @@
         <v>98.3</v>
       </c>
       <c r="P22">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -4876,7 +4891,7 @@
         <v>98.3</v>
       </c>
       <c r="X22">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Y22">
         <v>100</v>
@@ -4929,7 +4944,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -4953,7 +4968,7 @@
         <v>100</v>
       </c>
       <c r="X23">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Y23">
         <v>100</v>
@@ -5160,7 +5175,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -5184,7 +5199,7 @@
         <v>100</v>
       </c>
       <c r="X26">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="Y26">
         <v>100</v>
@@ -5237,7 +5252,7 @@
         <v>98.3</v>
       </c>
       <c r="P27">
-        <v>75</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -5261,7 +5276,7 @@
         <v>98.3</v>
       </c>
       <c r="X27">
-        <v>75</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Y27">
         <v>100</v>
@@ -5391,19 +5406,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>79.2</v>
+        <v>83.3</v>
       </c>
       <c r="G4" s="2">
-        <v>20.8</v>
+        <v>16.7</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5414,7 +5429,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>53</v>
@@ -5435,7 +5450,7 @@
         <v>4.2</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5446,7 +5461,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>54</v>
@@ -5455,19 +5470,19 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5613,7 +5628,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5645,16 +5660,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920043</v>
+        <v>23330051920181</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -5668,16 +5683,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920043</v>
+        <v>23330051920181</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -5691,39 +5706,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920029</v>
+        <v>22330051920007</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920031</v>
+        <v>22330051920007</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -5737,39 +5752,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920030</v>
+        <v>23330051920043</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920007</v>
+        <v>23330051920043</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -5783,36 +5798,36 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920033</v>
+        <v>23330051920212</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920034</v>
+        <v>23330051920212</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
         <v>97</v>
@@ -5829,13 +5844,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920232</v>
+        <v>23330051920029</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
         <v>98</v>
@@ -5852,10 +5867,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920035</v>
+        <v>23330051920031</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
         <v>84</v>
@@ -5875,10 +5890,10 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920032</v>
+        <v>23330051920030</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
         <v>85</v>
@@ -5898,10 +5913,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920039</v>
+        <v>23330051920033</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
         <v>86</v>
@@ -5921,13 +5936,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920040</v>
+        <v>23330051920034</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D14" t="s">
         <v>102</v>
@@ -5944,10 +5959,10 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920041</v>
+        <v>23330051920232</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
         <v>87</v>
@@ -5967,13 +5982,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920042</v>
+        <v>23330051920035</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
         <v>104</v>
@@ -5990,13 +6005,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920044</v>
+        <v>23330051920032</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
         <v>105</v>
@@ -6013,10 +6028,10 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920209</v>
+        <v>23330051920039</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
         <v>89</v>
@@ -6036,13 +6051,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920210</v>
+        <v>23330051920040</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
         <v>107</v>
@@ -6059,10 +6074,10 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920046</v>
+        <v>23330051920041</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
         <v>90</v>
@@ -6077,6 +6092,121 @@
         <v>50</v>
       </c>
       <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>23330051920042</v>
+      </c>
+      <c r="B21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>23330051920044</v>
+      </c>
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" t="s">
+        <v>50</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>23330051920209</v>
+      </c>
+      <c r="B23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s">
+        <v>50</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>23330051920210</v>
+      </c>
+      <c r="B24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" t="s">
+        <v>112</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>23330051920046</v>
+      </c>
+      <c r="B25" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" t="s">
+        <v>113</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" t="s">
+        <v>50</v>
+      </c>
+      <c r="G25">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3BEM - Estadisticos 20241.xlsx
+++ b/grupos/3BEM - Estadisticos 20241.xlsx
@@ -182,7 +182,7 @@
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>Castro Vasquez Julieta</t>
+    <t>Martínez Marañon Mauricio</t>
   </si>
   <si>
     <t>Marin Arzaba Roberto</t>

--- a/grupos/3BEM - Estadisticos 20241.xlsx
+++ b/grupos/3BEM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="84">
   <si>
     <t>Materia</t>
   </si>
@@ -176,12 +176,12 @@
     <t>Velasco Sánchez David</t>
   </si>
   <si>
+    <t>Martínez Marañon Mauricio</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>Martínez Marañon Mauricio</t>
-  </si>
-  <si>
     <t>Marin Arzaba Roberto</t>
   </si>
   <si>
@@ -212,18 +212,18 @@
     <t>MEJIA</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>VERA</t>
   </si>
   <si>
@@ -236,12 +236,12 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
     <t>SOLANO</t>
   </si>
   <si>
@@ -257,16 +257,16 @@
     <t>JOSE FRANCISCO</t>
   </si>
   <si>
+    <t>JESUS JAREF</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>IAN</t>
+  </si>
+  <si>
     <t>URIEL</t>
-  </si>
-  <si>
-    <t>JESUS JAREF</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>IAN</t>
   </si>
   <si>
     <t>ALEX URIEL</t>
@@ -817,28 +817,28 @@
         <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>8</v>
@@ -906,13 +906,13 @@
         <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -921,7 +921,7 @@
         <v>-1</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>-1</v>
@@ -933,7 +933,7 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z5">
         <v>7</v>
@@ -942,7 +942,7 @@
         <v>7</v>
       </c>
       <c r="AB5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC5">
         <v>5</v>
@@ -995,13 +995,13 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1010,7 +1010,7 @@
         <v>-1</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -1084,34 +1084,34 @@
         <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z7">
         <v>5</v>
@@ -1173,22 +1173,22 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>-1</v>
@@ -1200,16 +1200,16 @@
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z8">
         <v>6</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC8">
         <v>6</v>
@@ -1262,13 +1262,13 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1277,7 +1277,7 @@
         <v>-1</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
         <v>-1</v>
@@ -1351,13 +1351,13 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1366,19 +1366,19 @@
         <v>-1</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z10">
         <v>6</v>
@@ -1440,13 +1440,13 @@
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1455,13 +1455,13 @@
         <v>-1</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>9</v>
@@ -1529,13 +1529,13 @@
         <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1544,16 +1544,16 @@
         <v>-1</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -1618,13 +1618,13 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1633,19 +1633,19 @@
         <v>-1</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z13">
         <v>10</v>
@@ -1707,13 +1707,13 @@
         <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1722,13 +1722,13 @@
         <v>-1</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V14">
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -1796,13 +1796,13 @@
         <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1811,13 +1811,13 @@
         <v>-1</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -1832,7 +1832,7 @@
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC15">
         <v>5</v>
@@ -1885,13 +1885,13 @@
         <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -1900,13 +1900,13 @@
         <v>-1</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -1974,28 +1974,28 @@
         <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>9</v>
@@ -2010,7 +2010,7 @@
         <v>8</v>
       </c>
       <c r="AB17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC17">
         <v>5</v>
@@ -2063,13 +2063,13 @@
         <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2078,7 +2078,7 @@
         <v>-1</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>-1</v>
@@ -2087,7 +2087,7 @@
         <v>10</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -2099,7 +2099,7 @@
         <v>8</v>
       </c>
       <c r="AB18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC18">
         <v>9</v>
@@ -2152,13 +2152,13 @@
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2167,7 +2167,7 @@
         <v>-1</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>-1</v>
@@ -2241,22 +2241,22 @@
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -2330,28 +2330,28 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -2419,13 +2419,13 @@
         <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2434,7 +2434,7 @@
         <v>-1</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V22">
         <v>-1</v>
@@ -2508,34 +2508,34 @@
         <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z23">
         <v>5</v>
@@ -2582,7 +2582,7 @@
         <v>10</v>
       </c>
       <c r="K24">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L24">
         <v>7</v>
@@ -2597,13 +2597,13 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2612,7 +2612,7 @@
         <v>-1</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V24">
         <v>-1</v>
@@ -2624,7 +2624,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z24">
         <v>8</v>
@@ -2686,22 +2686,22 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>-1</v>
@@ -2775,13 +2775,13 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2790,13 +2790,13 @@
         <v>-1</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -2811,7 +2811,7 @@
         <v>8</v>
       </c>
       <c r="AB26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC26">
         <v>6</v>
@@ -2864,13 +2864,13 @@
         <v>7</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -2879,19 +2879,19 @@
         <v>-1</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>7</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z27">
         <v>5</v>
@@ -3075,7 +3075,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="P4">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -3087,10 +3087,10 @@
         <v>75.8</v>
       </c>
       <c r="T4">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="U4">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="V4">
         <v>84.09999999999999</v>
@@ -3155,10 +3155,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="T5">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="U5">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="V5">
         <v>97.7</v>
@@ -3223,7 +3223,7 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="U6">
         <v>100</v>
@@ -3291,10 +3291,10 @@
         <v>93.90000000000001</v>
       </c>
       <c r="T7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U7">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="V7">
         <v>95.5</v>
@@ -3359,7 +3359,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="T8">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U8">
         <v>100</v>
@@ -3427,7 +3427,7 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="U9">
         <v>100</v>
@@ -3495,10 +3495,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="T10">
-        <v>98</v>
+        <v>61.3</v>
       </c>
       <c r="U10">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="V10">
         <v>90.90000000000001</v>
@@ -3551,7 +3551,7 @@
         <v>95.5</v>
       </c>
       <c r="P11">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -3563,10 +3563,10 @@
         <v>93.90000000000001</v>
       </c>
       <c r="T11">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="U11">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="V11">
         <v>95.5</v>
@@ -3619,7 +3619,7 @@
         <v>97.7</v>
       </c>
       <c r="P12">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -3631,10 +3631,10 @@
         <v>93.90000000000001</v>
       </c>
       <c r="T12">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="U12">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="V12">
         <v>97.7</v>
@@ -3687,7 +3687,7 @@
         <v>93.2</v>
       </c>
       <c r="P13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -3699,10 +3699,10 @@
         <v>93.90000000000001</v>
       </c>
       <c r="T13">
-        <v>98</v>
+        <v>61.3</v>
       </c>
       <c r="U13">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="V13">
         <v>93.2</v>
@@ -3755,7 +3755,7 @@
         <v>97.7</v>
       </c>
       <c r="P14">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -3767,10 +3767,10 @@
         <v>93.90000000000001</v>
       </c>
       <c r="T14">
-        <v>98</v>
+        <v>61.3</v>
       </c>
       <c r="U14">
-        <v>99.2</v>
+        <v>99</v>
       </c>
       <c r="V14">
         <v>97.7</v>
@@ -3823,7 +3823,7 @@
         <v>93.2</v>
       </c>
       <c r="P15">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -3835,10 +3835,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="T15">
-        <v>98</v>
+        <v>61.3</v>
       </c>
       <c r="U15">
-        <v>98.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V15">
         <v>93.2</v>
@@ -3903,7 +3903,7 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -3959,7 +3959,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="P17">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -3971,10 +3971,10 @@
         <v>93.90000000000001</v>
       </c>
       <c r="T17">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="U17">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="V17">
         <v>88.59999999999999</v>
@@ -4027,7 +4027,7 @@
         <v>95.5</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -4039,10 +4039,10 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="U18">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V18">
         <v>95.5</v>
@@ -4107,10 +4107,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="T19">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="U19">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -4243,10 +4243,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="T21">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U21">
-        <v>99.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V21">
         <v>88.59999999999999</v>
@@ -4311,10 +4311,10 @@
         <v>97</v>
       </c>
       <c r="T22">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="U22">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="V22">
         <v>95.5</v>
@@ -4379,10 +4379,10 @@
         <v>84.8</v>
       </c>
       <c r="T23">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="U23">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="V23">
         <v>86.40000000000001</v>
@@ -4447,10 +4447,10 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="U24">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -4583,10 +4583,10 @@
         <v>81.8</v>
       </c>
       <c r="T26">
-        <v>98</v>
+        <v>61.3</v>
       </c>
       <c r="U26">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="V26">
         <v>93.2</v>
@@ -4651,10 +4651,10 @@
         <v>97</v>
       </c>
       <c r="T27">
-        <v>98</v>
+        <v>61.3</v>
       </c>
       <c r="U27">
-        <v>98.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V27">
         <v>86.40000000000001</v>
@@ -4778,7 +4778,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>52</v>
@@ -4787,19 +4787,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4810,7 +4810,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>53</v>
@@ -4831,7 +4831,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4927,7 +4927,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4997,7 +4997,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5167,7 +5167,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920045</v>
+        <v>23330051920181</v>
       </c>
       <c r="B8" t="s">
         <v>64</v>
@@ -5179,10 +5179,10 @@
         <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5190,22 +5190,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920045</v>
+        <v>22330051920007</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5213,16 +5213,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920181</v>
+        <v>23330051920043</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -5236,22 +5236,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920007</v>
+        <v>23330051920045</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5259,16 +5259,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920043</v>
+        <v>23330051920212</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -5277,29 +5277,6 @@
         <v>50</v>
       </c>
       <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920212</v>
-      </c>
-      <c r="B13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" t="s">
-        <v>83</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3BEM - Estadisticos 20241.xlsx
+++ b/grupos/3BEM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="61">
   <si>
     <t>Materia</t>
   </si>
@@ -170,15 +170,15 @@
     <t>Recursos socioemocionales III</t>
   </si>
   <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>Martínez Marañon Mauricio</t>
+  </si>
+  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Martínez Marañon Mauricio</t>
-  </si>
-  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
@@ -201,75 +201,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>IRVING</t>
-  </si>
-  <si>
-    <t>LEONEL</t>
-  </si>
-  <si>
-    <t>JOSE FRANCISCO</t>
-  </si>
-  <si>
-    <t>JESUS JAREF</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>IAN</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>ALEX URIEL</t>
   </si>
 </sst>
 </file>
@@ -826,7 +757,7 @@
         <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>8</v>
@@ -835,7 +766,7 @@
         <v>8</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>7</v>
@@ -847,7 +778,7 @@
         <v>7</v>
       </c>
       <c r="Z4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA4">
         <v>8</v>
@@ -856,7 +787,7 @@
         <v>7</v>
       </c>
       <c r="AC4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -915,16 +846,16 @@
         <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>10</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>9</v>
@@ -936,7 +867,7 @@
         <v>7</v>
       </c>
       <c r="Z5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA5">
         <v>7</v>
@@ -945,7 +876,7 @@
         <v>9</v>
       </c>
       <c r="AC5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1004,16 +935,16 @@
         <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -1025,7 +956,7 @@
         <v>7</v>
       </c>
       <c r="Z6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA6">
         <v>8</v>
@@ -1093,7 +1024,7 @@
         <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>8</v>
@@ -1102,7 +1033,7 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -1114,7 +1045,7 @@
         <v>8</v>
       </c>
       <c r="Z7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA7">
         <v>7</v>
@@ -1182,7 +1113,7 @@
         <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>7</v>
@@ -1191,7 +1122,7 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1203,7 +1134,7 @@
         <v>7</v>
       </c>
       <c r="Z8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA8">
         <v>7</v>
@@ -1271,16 +1202,16 @@
         <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
         <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1360,16 +1291,16 @@
         <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>8</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1381,7 +1312,7 @@
         <v>8</v>
       </c>
       <c r="Z10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA10">
         <v>8</v>
@@ -1449,16 +1380,16 @@
         <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -1470,10 +1401,10 @@
         <v>9</v>
       </c>
       <c r="Z11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB11">
         <v>8</v>
@@ -1538,16 +1469,16 @@
         <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>8</v>
@@ -1559,16 +1490,16 @@
         <v>9</v>
       </c>
       <c r="Z12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB12">
         <v>8</v>
       </c>
       <c r="AC12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1627,16 +1558,16 @@
         <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>8</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1716,16 +1647,16 @@
         <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>9</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1805,16 +1736,16 @@
         <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>9</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -1826,7 +1757,7 @@
         <v>8</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA15">
         <v>8</v>
@@ -1835,7 +1766,7 @@
         <v>8</v>
       </c>
       <c r="AC15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1894,16 +1825,16 @@
         <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U16">
         <v>10</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>8</v>
@@ -1924,7 +1855,7 @@
         <v>9</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1983,7 +1914,7 @@
         <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>9</v>
@@ -1992,7 +1923,7 @@
         <v>9</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2004,7 +1935,7 @@
         <v>8</v>
       </c>
       <c r="Z17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA17">
         <v>8</v>
@@ -2013,7 +1944,7 @@
         <v>8</v>
       </c>
       <c r="AC17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2072,16 +2003,16 @@
         <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>7</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>10</v>
@@ -2093,10 +2024,10 @@
         <v>10</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB18">
         <v>7</v>
@@ -2161,16 +2092,16 @@
         <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>8</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>10</v>
@@ -2185,13 +2116,13 @@
         <v>10</v>
       </c>
       <c r="AA19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB19">
         <v>9</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2250,7 +2181,7 @@
         <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2259,7 +2190,7 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>9</v>
@@ -2339,7 +2270,7 @@
         <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>7</v>
@@ -2348,7 +2279,7 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2360,7 +2291,7 @@
         <v>8</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>8</v>
@@ -2428,16 +2359,16 @@
         <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>9</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2517,7 +2448,7 @@
         <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>7</v>
@@ -2526,7 +2457,7 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>7</v>
@@ -2538,7 +2469,7 @@
         <v>7</v>
       </c>
       <c r="Z23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA23">
         <v>7</v>
@@ -2547,7 +2478,7 @@
         <v>7</v>
       </c>
       <c r="AC23">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2606,16 +2537,16 @@
         <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>9</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -2627,7 +2558,7 @@
         <v>10</v>
       </c>
       <c r="Z24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA24">
         <v>8</v>
@@ -2695,7 +2626,7 @@
         <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2704,7 +2635,7 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2784,16 +2715,16 @@
         <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>7</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W26">
         <v>8</v>
@@ -2805,10 +2736,10 @@
         <v>7</v>
       </c>
       <c r="Z26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB26">
         <v>7</v>
@@ -2873,16 +2804,16 @@
         <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <v>8</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W27">
         <v>7</v>
@@ -2894,7 +2825,7 @@
         <v>8</v>
       </c>
       <c r="Z27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA27">
         <v>7</v>
@@ -3084,7 +3015,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>75.8</v>
+        <v>81.3</v>
       </c>
       <c r="T4">
         <v>98.8</v>
@@ -3093,7 +3024,7 @@
         <v>99.5</v>
       </c>
       <c r="V4">
-        <v>84.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3152,16 +3083,16 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="T5">
-        <v>60</v>
+        <v>96.3</v>
       </c>
       <c r="U5">
         <v>99</v>
       </c>
       <c r="V5">
-        <v>97.7</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3220,16 +3151,16 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T6">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="U6">
         <v>100</v>
       </c>
       <c r="V6">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3288,7 +3219,7 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="T7">
         <v>97.5</v>
@@ -3297,7 +3228,7 @@
         <v>99.5</v>
       </c>
       <c r="V7">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -3356,7 +3287,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="T8">
         <v>97.5</v>
@@ -3427,7 +3358,7 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="U9">
         <v>100</v>
@@ -3492,16 +3423,16 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>90.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="T10">
-        <v>61.3</v>
+        <v>97.5</v>
       </c>
       <c r="U10">
         <v>99</v>
       </c>
       <c r="V10">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3560,16 +3491,16 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>93.90000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="T11">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="U11">
         <v>99</v>
       </c>
       <c r="V11">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3628,16 +3559,16 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>93.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="T12">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="U12">
         <v>99</v>
       </c>
       <c r="V12">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3696,16 +3627,16 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="T13">
-        <v>61.3</v>
+        <v>97.5</v>
       </c>
       <c r="U13">
         <v>99</v>
       </c>
       <c r="V13">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -3764,16 +3695,16 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>93.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="T14">
-        <v>61.3</v>
+        <v>96.3</v>
       </c>
       <c r="U14">
         <v>99</v>
       </c>
       <c r="V14">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3832,16 +3763,16 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>90.90000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="T15">
-        <v>61.3</v>
+        <v>97.5</v>
       </c>
       <c r="U15">
         <v>98.40000000000001</v>
       </c>
       <c r="V15">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -3903,13 +3834,13 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="U16">
         <v>100</v>
       </c>
       <c r="V16">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -3968,7 +3899,7 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>93.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="T17">
         <v>98.8</v>
@@ -3977,7 +3908,7 @@
         <v>99.5</v>
       </c>
       <c r="V17">
-        <v>88.59999999999999</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -4036,16 +3967,16 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T18">
-        <v>62.5</v>
+        <v>97.5</v>
       </c>
       <c r="U18">
         <v>97.90000000000001</v>
       </c>
       <c r="V18">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4104,10 +4035,10 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>90.90000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="T19">
-        <v>62.5</v>
+        <v>98.8</v>
       </c>
       <c r="U19">
         <v>99.5</v>
@@ -4172,7 +4103,7 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>97</v>
+        <v>93.8</v>
       </c>
       <c r="T20">
         <v>100</v>
@@ -4240,7 +4171,7 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="T21">
         <v>97.5</v>
@@ -4249,7 +4180,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="V21">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -4308,16 +4239,16 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>97</v>
+        <v>91.7</v>
       </c>
       <c r="T22">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="U22">
         <v>99</v>
       </c>
       <c r="V22">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -4376,7 +4307,7 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>84.8</v>
+        <v>81.3</v>
       </c>
       <c r="T23">
         <v>95</v>
@@ -4385,7 +4316,7 @@
         <v>99</v>
       </c>
       <c r="V23">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -4447,7 +4378,7 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>62.5</v>
+        <v>98.8</v>
       </c>
       <c r="U24">
         <v>99.5</v>
@@ -4580,16 +4511,16 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>81.8</v>
+        <v>81.3</v>
       </c>
       <c r="T26">
-        <v>61.3</v>
+        <v>96.3</v>
       </c>
       <c r="U26">
         <v>99</v>
       </c>
       <c r="V26">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -4648,16 +4579,16 @@
         <v>100</v>
       </c>
       <c r="S27">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="T27">
-        <v>61.3</v>
+        <v>96.3</v>
       </c>
       <c r="U27">
         <v>98.40000000000001</v>
       </c>
       <c r="V27">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -4714,7 +4645,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>50</v>
@@ -4723,19 +4654,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>70.8</v>
+        <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>29.2</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4746,7 +4677,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>51</v>
@@ -4755,19 +4686,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4778,7 +4709,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>52</v>
@@ -4799,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4863,7 +4794,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4997,7 +4928,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5027,259 +4958,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920028</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920028</v>
-      </c>
-      <c r="B3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920037</v>
-      </c>
-      <c r="B4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920037</v>
-      </c>
-      <c r="B5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920021</v>
-      </c>
-      <c r="B6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920021</v>
-      </c>
-      <c r="B7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920181</v>
-      </c>
-      <c r="B8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920007</v>
-      </c>
-      <c r="B9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920043</v>
-      </c>
-      <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920045</v>
-      </c>
-      <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920212</v>
-      </c>
-      <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
